--- a/docs/workbook-split/dateien/D KLR.xlsx
+++ b/docs/workbook-split/dateien/D KLR.xlsx
@@ -59261,6 +59261,8 @@
         <v>42</v>
       </c>
     </row>
+    <row r="1147"/>
+    <row r="1148"/>
     <row r="1149">
       <c r="C1149" t="inlineStr">
         <is>
